--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N41_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.9188376542076</v>
+        <v>6.649311118808735</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5318180825699</v>
+        <v>2.36142043841761</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
